--- a/results/job_matches_2026-06-06.xlsx
+++ b/results/job_matches_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Trianz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Clinton, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ff12a0a5a571cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4383b83bebf58ee2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Solutions Architect – Azure Databricks</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MINDBRIDGE SOLUTIONS INC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e70c6ae374fe7d</t>
+          <t>https://www.indeed.com/viewjob?jk=53ff12a0a5a571cd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Data Solutions Architect – Azure Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MINDBRIDGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b03d7c92e1f21c5</t>
+          <t>https://www.indeed.com/viewjob?jk=31e70c6ae374fe7d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5772ff395b2cde45</t>
+          <t>https://www.indeed.com/viewjob?jk=4b03d7c92e1f21c5</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>New York Blood Center</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Rye, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b877f69f2d40c</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ReactJS with Azure developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Platform Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>ActiveProspect, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
+          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Manscaped</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Bluebird Fiber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Independence, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
+          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer - Power BI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Independence, OH, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
+          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Power BI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Madagoni LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eaba1f6b997fc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Madagoni LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Spark, PySpark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
+          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Palm Tree</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Integration Technical Architect (AWS/AI)</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, DynamoDB</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eff26eac5f1144c</t>
+          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Radian Group Inc.</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7404c3655de04dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bcd1876902912f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9b38178b754383</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82b6e9e211f61d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a620a55e826a673d</t>
+          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902e213debac8809</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1016648c0f0d5d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc1d5f8003f7600</t>
+          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fbd56cbb6e1afe</t>
+          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17103584ffb6e509</t>
+          <t>https://www.indeed.com/viewjob?jk=7404c3655de04dd7</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cd476fc679a04a</t>
+          <t>https://www.indeed.com/viewjob?jk=3bcd1876902912f2</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb9b103396ef75e</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9b38178b754383</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1885c3e7464f9bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=e82b6e9e211f61d4</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8189bb7df0daff</t>
+          <t>https://www.indeed.com/viewjob?jk=a620a55e826a673d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d53b87a5ed021b7</t>
+          <t>https://www.indeed.com/viewjob?jk=902e213debac8809</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85395c75059dc994</t>
+          <t>https://www.indeed.com/viewjob?jk=1016648c0f0d5d0b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b92f217fa630744</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc1d5f8003f7600</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8564e7eebd81568f</t>
+          <t>https://www.indeed.com/viewjob?jk=74fbd56cbb6e1afe</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c751ca8403940e46</t>
+          <t>https://www.indeed.com/viewjob?jk=17103584ffb6e509</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec5266cd24c2dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cd476fc679a04a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265bf1290caccb77</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb9b103396ef75e</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24914a82cfe666e</t>
+          <t>https://www.indeed.com/viewjob?jk=1885c3e7464f9bc2</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05705973a9378d80</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8189bb7df0daff</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795911acb1bee51f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d53b87a5ed021b7</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0942fc02191a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=85395c75059dc994</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=617495dbf623e38c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b92f217fa630744</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52f3fc7ec6df2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8564e7eebd81568f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b93989e7d84</t>
+          <t>https://www.indeed.com/viewjob?jk=c751ca8403940e46</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4581cdcaed5f9f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec5266cd24c2dd6</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c766afcec299ad51</t>
+          <t>https://www.indeed.com/viewjob?jk=265bf1290caccb77</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cb2c150ee12d87</t>
+          <t>https://www.indeed.com/viewjob?jk=d24914a82cfe666e</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d75093b6fcd02c5</t>
+          <t>https://www.indeed.com/viewjob?jk=05705973a9378d80</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676f9ebac1172832</t>
+          <t>https://www.indeed.com/viewjob?jk=795911acb1bee51f</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454de9f58fa31614</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0942fc02191a0c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba87ffa60d4ea16b</t>
+          <t>https://www.indeed.com/viewjob?jk=617495dbf623e38c</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=954bc66fa74e678c</t>
+          <t>https://www.indeed.com/viewjob?jk=e52f3fc7ec6df2ba</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3adae39628854eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b93989e7d84</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a7a440e90ffe87a</t>
+          <t>https://www.indeed.com/viewjob?jk=4581cdcaed5f9f0c</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd03d55c286c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c766afcec299ad51</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e7399fcd292254</t>
+          <t>https://www.indeed.com/viewjob?jk=77cb2c150ee12d87</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693602db725cd736</t>
+          <t>https://www.indeed.com/viewjob?jk=7d75093b6fcd02c5</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059b9c50895f7fee</t>
+          <t>https://www.indeed.com/viewjob?jk=676f9ebac1172832</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e189e5672a8c8a33</t>
+          <t>https://www.indeed.com/viewjob?jk=454de9f58fa31614</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9c5376661bd35b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba87ffa60d4ea16b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adba19e5f6f34e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=954bc66fa74e678c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0494adf7cd3b47d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d3adae39628854eb</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a0794cdf7814e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a7a440e90ffe87a</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd03a4989d1f2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd03d55c286c7fd</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77011faf16332680</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e7399fcd292254</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,77 +3251,77 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=693602db725cd736</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
+          <t>https://www.indeed.com/viewjob?jk=059b9c50895f7fee</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TG Administration LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
+          <t>https://www.indeed.com/viewjob?jk=e189e5672a8c8a33</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
+          <t>https://www.indeed.com/viewjob?jk=de9c5376661bd35b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SDET AI Architect role</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nexzentek</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169be2658178cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=adba19e5f6f34e9a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BI and AI Automation Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Trianz</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,102 +3436,102 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063c5940585caea</t>
+          <t>https://www.indeed.com/viewjob?jk=0494adf7cd3b47d6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a0794cdf7814e0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate - Full Stack Developer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
+          <t>https://www.indeed.com/viewjob?jk=edd03a4989d1f2d2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
+          <t>https://www.indeed.com/viewjob?jk=77011faf16332680</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sunward</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3597,46 +3597,46 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
+          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>TG Administration LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
+          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tyto Athene</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Business Analyst, Senior Associate</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
+          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angeles</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>SDET AI Architect role</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Nexzentek</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,54 +3821,54 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
+          <t>https://www.indeed.com/viewjob?jk=c169be2658178cd6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>URBN Senior DevOps Engineer</t>
+          <t>Associate - Full Stack Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>URBN</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3877,11 +3877,11 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
+          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Qnity</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,67 +3926,67 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
+          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer Associate</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Sunward</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Roseville, CA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
+          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Child Mind Institute</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,172 +3996,172 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Analyst, Senior Associate</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Managed Services Engineer III</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angeles</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Python Web Application Developer</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IntelliDyne</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,59 +4206,59 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68462d5c7447b1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>URBN Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>URBN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer I- Operations</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Utah Valley University</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafdc7b6e7a9e469</t>
+          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Scientist - Sr. Associate - Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
+          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sfklogix LLC</t>
+          <t>Qnity</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Roseville, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
+          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
+          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
+          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Distinguished Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
+          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
+          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Python Web Application Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>IntelliDyne</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=68462d5c7447b1bc</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
+          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Site Reliability Engineer I- Operations</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Utah Valley University</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
+          <t>https://www.indeed.com/viewjob?jk=aafdc7b6e7a9e469</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Data Scientist - Sr. Associate - Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
+          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
+          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
+          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
+          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
+          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
+          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
+          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
+          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
+          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
+          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
+          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
+          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
+          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,392 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
+          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
           <t>https://www.indeed.com/viewjob?jk=fdc98d9c47321a48</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sfklogix LLC</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-06.xlsx
+++ b/results/job_matches_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b03d7c92e1f21c5</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML Architect with Databricks , AWS</t>
+          <t>Sr Data Engineer- Data Platform &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=830c3438f0d2663d</t>
+          <t>https://www.indeed.com/viewjob?jk=18c6ead6041dd8b2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc95db0c4e95e26</t>
+          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (.NET / Azure)</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69f8437775af7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New York Blood Center</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rye, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc95db0c4e95e26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (.NET / Azure)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=e69f8437775af7c1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate ETL Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>New York Blood Center</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Rye, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Associate ETL Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f7a82ae76adde3</t>
+          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=02f7a82ae76adde3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DevOps)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ActiveProspect, Inc.</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
+          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Platform Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>ActiveProspect, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
+          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Independence, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
+          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Power BI</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Bluebird Fiber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
+          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Madagoni LLC</t>
+          <t>Bluebird Fiber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Independence, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
+          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Power BI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
+          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Madagoni LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
+          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Platform Integration Engineer (Senior Associate)</t>
+          <t>Cloud DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ffac673f9e5e45</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d21417725ec301b</t>
+          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Platform Integration Engineer (Senior Associate)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=21ffac673f9e5e45</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Palm Tree</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=5d21417725ec301b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Palm Tree</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
+          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
+          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
+          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
+          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
+          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
         </is>
       </c>
     </row>
@@ -3688,17 +3688,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
+          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>SDET AI Architect role</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Nexzentek</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=c169be2658178cd6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SDET AI Architect role</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nexzentek</t>
+          <t>Tyto Athene</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169be2658178cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
+          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Business Analyst, Senior Associate</t>
+          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
+          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Business Analyst, Senior Associate</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
+          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angeles</t>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angeles</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
+          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Distinguished Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
+          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, Data Platform</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
+          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Python Web Application Developer</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IntelliDyne</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68462d5c7447b1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Site Reliability Engineer I- Operations</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Utah Valley University</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=aafdc7b6e7a9e469</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer I- Operations</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Utah Valley University</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafdc7b6e7a9e469</t>
+          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Scientist - Sr. Associate - Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
+          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
+          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
+          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
+          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
+          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
+          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
+          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
+          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
+          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
+          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
+          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
+          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
+          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
+          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
+          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
+          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
+          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
+          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
+          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc98d9c47321a48</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Sfklogix LLC</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
+          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,85 +5946,15 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc98d9c47321a48</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Sfklogix LLC</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Fort Meade, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
         </is>

--- a/results/job_matches_2026-06-06.xlsx
+++ b/results/job_matches_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Sr Data Engineer- Data Platform &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
+          <t>https://www.indeed.com/viewjob?jk=18c6ead6041dd8b2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer- Data Platform &amp; AI Enablement</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c6ead6041dd8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate ETL Developer</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>Associate ETL Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
+          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
+          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer - Power BI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
+          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Independence, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
+          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Power BI</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Bluebird Fiber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Independence, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
+          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Madagoni LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
+          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer (Remote)</t>
+          <t>Data Platform Integration Engineer (Senior Associate)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=21ffac673f9e5e45</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
+          <t>https://www.indeed.com/viewjob?jk=5d21417725ec301b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Integration Engineer (Senior Associate)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Madagoni LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ffac673f9e5e45</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d21417725ec301b</t>
+          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
         </is>
       </c>
     </row>
@@ -1833,25 +1833,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Senior Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7404c3655de04dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bcd1876902912f2</t>
+          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TG Administration LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9b38178b754383</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82b6e9e211f61d4</t>
+          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a620a55e826a673d</t>
+          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902e213debac8809</t>
+          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>SDET AI Architect role</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Nexzentek</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1016648c0f0d5d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=c169be2658178cd6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tyto Athene</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,102 +2106,102 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc1d5f8003f7600</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fbd56cbb6e1afe</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Associate - Full Stack Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17103584ffb6e509</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cd476fc679a04a</t>
+          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb9b103396ef75e</t>
+          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1885c3e7464f9bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8189bb7df0daff</t>
+          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d53b87a5ed021b7</t>
+          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85395c75059dc994</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b92f217fa630744</t>
+          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Business Analyst, Senior Associate</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8564e7eebd81568f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c751ca8403940e46</t>
+          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec5266cd24c2dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Qnity</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265bf1290caccb77</t>
+          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Roseville, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24914a82cfe666e</t>
+          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05705973a9378d80</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795911acb1bee51f</t>
+          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Distinguished Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0942fc02191a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=617495dbf623e38c</t>
+          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52f3fc7ec6df2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Site Reliability Engineer I- Operations</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Utah Valley University</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b93989e7d84</t>
+          <t>https://www.indeed.com/viewjob?jk=aafdc7b6e7a9e469</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sfklogix LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4581cdcaed5f9f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c766afcec299ad51</t>
+          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,3052 +2911,1267 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cb2c150ee12d87</t>
+          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d75093b6fcd02c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676f9ebac1172832</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454de9f58fa31614</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba87ffa60d4ea16b</t>
+          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=954bc66fa74e678c</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3adae39628854eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a7a440e90ffe87a</t>
+          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd03d55c286c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e7399fcd292254</t>
+          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693602db725cd736</t>
+          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059b9c50895f7fee</t>
+          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e189e5672a8c8a33</t>
+          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9c5376661bd35b</t>
+          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adba19e5f6f34e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0494adf7cd3b47d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a0794cdf7814e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd03a4989d1f2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77011faf16332680</t>
+          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Kafka Platform Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
+          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TG Administration LLC</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
+          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
+          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
+          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SDET AI Architect role</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nexzentek</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169be2658178cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
+          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Associate - Full Stack Developer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
+          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
+          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sunward</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
+          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
+          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Business Analyst, Senior Associate</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
+          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angeles</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Portfolio BI</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>URBN Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>URBN</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>ASM</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>ASM</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Qnity</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Data Engineer Associate</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Bosch</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Roseville, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Child Mind Institute</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Engineer Intern/Co-op</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Distinguished Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>CloudZero</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>People Analytics AI Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>HR -Data Scientist</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>People Analytics AI Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer I- Operations</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Utah Valley University</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Orem, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aafdc7b6e7a9e469</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>WV, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>WY, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>SC, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>UT, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>VT, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>WI, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>ND, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>AL, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>NE, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>OK, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>ME, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>PA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>IA, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>MN, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>SD, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>KS, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>LA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>RI, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>NM, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>MS, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>NV, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>ID, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>MI, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=fdc98d9c47321a48</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Sfklogix LLC</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Fort Meade, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-06.xlsx
+++ b/results/job_matches_2026-06-06.xlsx
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Database Engineer/Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ron turley associates</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Glendale, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ff12a0a5a571cd</t>
+          <t>https://www.indeed.com/viewjob?jk=38fb9ceb49a96b57</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Solutions Architect – Azure Databricks</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MINDBRIDGE SOLUTIONS INC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e70c6ae374fe7d</t>
+          <t>https://www.indeed.com/viewjob?jk=53ff12a0a5a571cd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Architect – Azure Databricks</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>MINDBRIDGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
+          <t>https://www.indeed.com/viewjob?jk=31e70c6ae374fe7d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Engineer- Data Platform &amp; AI Enablement</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c6ead6041dd8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Sr Data Engineer- Data Platform &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
+          <t>https://www.indeed.com/viewjob?jk=18c6ead6041dd8b2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
         </is>
       </c>
     </row>
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
+          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc95db0c4e95e26</t>
+          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (.NET / Azure)</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69f8437775af7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc95db0c4e95e26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (.NET / Azure)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New York Blood Center</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rye, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e69f8437775af7c1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>New York Blood Center</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Rye, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate ETL Developer</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Associate ETL Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f7a82ae76adde3</t>
+          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Madagoni LLC</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
+          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Palm Tree</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
+          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Palm Tree</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
+          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
+          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
+          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
+          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
+          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SDET AI Architect role</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexzentek</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169be2658178cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
+          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
+          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
+          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Business Analyst, Senior Associate</t>
+          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
+          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>Business Analyst, Senior Associate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
         </is>
       </c>
     </row>
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
+          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Qnity</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
+          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer Associate</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Qnity</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Roseville, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
+          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Child Mind Institute</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Roseville, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
+          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,29 +2656,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, Data Platform</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
+          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Distinguished Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
+          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer I- Operations</t>
+          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Utah Valley University</t>
+          <t>Sfklogix LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafdc7b6e7a9e469</t>
+          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sfklogix LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
+          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-06.xlsx
+++ b/results/job_matches_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Database Engineer/Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trianz</t>
+          <t>ron turley associates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Clinton, NJ, US USA</t>
+          <t>Glendale, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4383b83bebf58ee2</t>
+          <t>https://www.indeed.com/viewjob?jk=38fb9ceb49a96b57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Database Engineer/Architect</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ron turley associates</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Glendale, AZ, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38fb9ceb49a96b57</t>
+          <t>https://www.indeed.com/viewjob?jk=53ff12a0a5a571cd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Solutions Architect – Azure Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>MINDBRIDGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ff12a0a5a571cd</t>
+          <t>https://www.indeed.com/viewjob?jk=31e70c6ae374fe7d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Solutions Architect – Azure Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MINDBRIDGE SOLUTIONS INC</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e70c6ae374fe7d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
         </is>
       </c>
     </row>
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure, Kafka</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
         </is>
       </c>
     </row>
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc95db0c4e95e26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Senior Data Engineer (.NET / Azure)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc95db0c4e95e26</t>
+          <t>https://www.indeed.com/viewjob?jk=e69f8437775af7c1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (.NET / Azure)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>New York Blood Center</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rye, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69f8437775af7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New York Blood Center</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rye, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>Associate ETL Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
+          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
+          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>ActiveProspect, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
+          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DevOps)</t>
+          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ActiveProspect, Inc.</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
+          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Bluebird Fiber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Power BI</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Bluebird Fiber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Independence, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
+          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer - Power BI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,42 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
+          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Independence, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
+          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Palm Tree</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
+          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Palm Tree</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
+          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
+          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
+          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,64 +1781,64 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
+          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
+          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Kafka Platform Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
+          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>TG Administration LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TG Administration LLC</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
+          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
+          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Tyto Athene</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,104 +2096,104 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
+          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate - Full Stack Developer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
+          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
+          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
+          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
+          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
+          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
+          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
+          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Business Analyst, Senior Associate</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Qnity</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2477,11 +2477,11 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
+          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Roseville, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Qnity</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
+          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer Associate</t>
+          <t>Distinguished Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Roseville, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
+          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Child Mind Institute</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
+          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
+          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, Data Platform</t>
+          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Sfklogix LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
+          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sfklogix LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
+          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
+          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
+          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
+          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
+          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
+          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
+          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
+          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
+          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
+          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
+          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
+          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
+          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
+          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
+          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
+          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
+          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
+          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
+          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
+          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4065,111 +4065,6 @@
         </is>
       </c>
       <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>ID, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>MI, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fdc98d9c47321a48</t>
         </is>

--- a/results/job_matches_2026-06-06.xlsx
+++ b/results/job_matches_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ff12a0a5a571cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Solutions Architect – Azure Databricks</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MINDBRIDGE SOLUTIONS INC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e70c6ae374fe7d</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
+          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure, Kafka</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
+          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer- Data Platform &amp; AI Enablement</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c6ead6041dd8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc95db0c4e95e26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>Senior Data Engineer (.NET / Azure)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e69f8437775af7c1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>New York Blood Center</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rye, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc95db0c4e95e26</t>
+          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (.NET / Azure)</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69f8437775af7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate ETL Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New York Blood Center</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rye, NY, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
+          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>Senior Platform Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>ActiveProspect, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate ETL Developer</t>
+          <t>Senior Data Engineer - Power BI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
+          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>Bluebird Fiber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
+          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>Bluebird Fiber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Independence, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DevOps)</t>
+          <t>Cloud DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ActiveProspect, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Platform Integration Engineer (Senior Associate)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
+          <t>https://www.indeed.com/viewjob?jk=21ffac673f9e5e45</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Independence, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
+          <t>https://www.indeed.com/viewjob?jk=5d21417725ec301b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Power BI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
+          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
+          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer (Remote)</t>
+          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Palm Tree</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
+          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Platform Integration Engineer (Senior Associate)</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ffac673f9e5e45</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d21417725ec301b</t>
+          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Palm Tree</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
+          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
+          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
+          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Senior Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
+          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
+          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>TG Administration LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
+          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Kafka Platform Engineer</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
+          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TG Administration LLC</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
+          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Tyto Athene</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
+          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
+          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
+          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
+          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
+          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Qnity</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
+          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Roseville, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
+          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
+          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
+          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Qnity</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer Associate</t>
+          <t>Distinguished Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Roseville, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
+          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Child Mind Institute</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
+          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
+          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, Data Platform</t>
+          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Sfklogix LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
+          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sfklogix LLC</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
+          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
+          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
+          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
+          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
+          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
+          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
+          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
+          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
+          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
+          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
+          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
+          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
+          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
+          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
+          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
+          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
+          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
+          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
+          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
+          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3960,111 +3960,6 @@
         </is>
       </c>
       <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>ID, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>MI, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fdc98d9c47321a48</t>
         </is>

--- a/results/job_matches_2026-06-06.xlsx
+++ b/results/job_matches_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,52 +853,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>SmithRx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d83253303e037541</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DevOps)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ActiveProspect, Inc.</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
+          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Power BI</t>
+          <t>Senior Platform Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>ActiveProspect, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
+          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
+          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer - Power BI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
+          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Independence, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
+          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer (Remote)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bluebird Fiber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Independence, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Platform Integration Engineer (Senior Associate)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ffac673f9e5e45</t>
+          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Data Platform Integration Engineer (Senior Associate)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d21417725ec301b</t>
+          <t>https://www.indeed.com/viewjob?jk=21ffac673f9e5e45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
+          <t>https://www.indeed.com/viewjob?jk=5d21417725ec301b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
+          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Palm Tree</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
+          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Palm Tree</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
+          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
+          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
+          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
+          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Kafka Platform Engineer</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
+          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>SmithRx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
+          <t>https://www.indeed.com/viewjob?jk=a26b1a617031dc58</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TG Administration LLC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
+          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
+          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>TG Administration LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
+          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Tyto Athene</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
+          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
+          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
+          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
+          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>Business Services Developer (Business Services Analyst)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>County of Orange</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
+          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Qnity</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
+          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer Associate</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Roseville, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
+          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Child Mind Institute</t>
+          <t>Qnity</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
+          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Roseville, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
+          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,29 +2481,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, Data Platform</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
+          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Distinguished Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sfklogix LLC</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
+          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sfklogix LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
+          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
+          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
+          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
+          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
+          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
+          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
+          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
+          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
+          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
+          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
+          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
+          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
+          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
+          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
+          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
+          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
+          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
+          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
+          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
+          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
+          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
+          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
+          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
         </is>
       </c>
     </row>
@@ -3943,23 +3943,58 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
           <t>MI, US USA</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fdc98d9c47321a48</t>
         </is>

--- a/results/job_matches_2026-06-06.xlsx
+++ b/results/job_matches_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Confluent Kafka Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>NSV IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
+          <t>https://www.indeed.com/viewjob?jk=3731032ae0f7a545</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure, Kafka</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
         </is>
       </c>
     </row>
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
+          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc95db0c4e95e26</t>
+          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (.NET / Azure)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>New York Blood Center</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rye, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69f8437775af7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New York Blood Center</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rye, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate ETL Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>OpenText xECM Administrator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,46 +797,46 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
+          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate ETL Developer</t>
+          <t>Senior Platform Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>ActiveProspect, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
+          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer - Power BI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SmithRx</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83253303e037541</t>
+          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>Bluebird Fiber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DevOps)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ActiveProspect, Inc.</t>
+          <t>Bluebird Fiber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Independence, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
+          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Power BI</t>
+          <t>Cloud DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,94 +986,94 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
+          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Independence, OH, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
+          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer (Remote)</t>
+          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Palm Tree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
+          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Platform Integration Engineer (Senior Associate)</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ffac673f9e5e45</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d21417725ec301b</t>
+          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Palm Tree</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
+          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
+          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Senior Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
+          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
+          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>TG Administration LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
+          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
+          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SmithRx</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26b1a617031dc58</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Kafka Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Tyto Athene</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
+          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TG Administration LLC</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
+          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Business Services Developer (Business Services Analyst)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>County of Orange</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
+          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
+          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2057,11 +2057,11 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
+          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
+          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Qnity</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
+          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
+          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Distinguished Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
+          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
+          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Business Services Developer (Business Services Analyst)</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>County of Orange</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
+          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>Sfklogix LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,1652 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>ASM</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Qnity</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Data Engineer Associate</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Bosch</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Roseville, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Child Mind Institute</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Data Engineer Intern/Co-op</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Distinguished Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>CloudZero</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>People Analytics AI Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Sfklogix LLC</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Fort Meade, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>HR -Data Scientist</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>WV, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>WY, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>SC, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>UT, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>VT, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>WI, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ND, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AL, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>NE, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>OK, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>ME, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>PA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>IA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>MN, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>SD, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>KS, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>LA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>RI, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>NM, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>MS, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>NV, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>ID, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>MI, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc98d9c47321a48</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-06.xlsx
+++ b/results/job_matches_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Database Engineer/Architect</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ron turley associates</t>
+          <t>Trianz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Glendale, AZ, US USA</t>
+          <t>Clinton, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38fb9ceb49a96b57</t>
+          <t>https://www.indeed.com/viewjob?jk=4383b83bebf58ee2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Confluent Kafka Architect</t>
+          <t>Database Engineer/Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>ron turley associates</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3731032ae0f7a545</t>
+          <t>https://www.indeed.com/viewjob?jk=38fb9ceb49a96b57</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Confluent Kafka Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>NSV IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
+          <t>https://www.indeed.com/viewjob?jk=3731032ae0f7a545</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure, Kafka</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate ETL Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,54 +741,54 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate ETL Developer</t>
+          <t>OpenText xECM Administrator</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
+          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OpenText xECM Administrator</t>
+          <t>Senior Platform Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ActiveProspect, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
+          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DevOps)</t>
+          <t>Senior Data Engineer - Power BI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ActiveProspect, Inc.</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
+          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Power BI</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Bluebird Fiber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
+          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Independence, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
+          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Independence, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
+          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
+          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
         </is>
       </c>
     </row>
@@ -1098,25 +1098,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Senior Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
+          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
+          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
+          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
+          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Tyto Athene</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
+          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
+          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineering - Agentic AI Engineer (Junior)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aline</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Kafka, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Services Developer (Business Services Analyst)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>County of Orange</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Kafka Platform Engineer</t>
+          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
+          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
+          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TG Administration LLC</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
+          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
+          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Distinguished Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,54 +1686,54 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
+          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>Sfklogix LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1755,601 +1755,6 @@
         </is>
       </c>
       <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Full Stack Data Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Foxconn Industrial Internet - FII</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Staples</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Framingham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Business Services Developer (Business Services Analyst)</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>County of Orange</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior .net Software Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>BlackRock</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>ASM</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>ASM</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Qnity</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Child Mind Institute</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Distinguished Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>CloudZero</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>People Analytics AI Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>HR -Data Scientist</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Sfklogix LLC</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
         </is>

--- a/results/job_matches_2026-06-06.xlsx
+++ b/results/job_matches_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,47 +713,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate ETL Developer</t>
+          <t>OpenText xECM Administrator</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
+          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OpenText xECM Administrator</t>
+          <t>Senior Platform Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ActiveProspect, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,29 +766,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
+          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DevOps)</t>
+          <t>Cloud DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ActiveProspect, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Power BI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
+          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec84abb9723f3323</t>
+          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bluebird Fiber</t>
+          <t>Palm Tree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Independence, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6038be7764e9b130</t>
+          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,147 +941,147 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
+          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
+          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Palm Tree</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Kafka Platform Engineer</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Tyto Athene</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
+          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
+          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
+          <t>Business Services Developer (Business Services Analyst)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>County of Orange</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
+          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Business Services Developer (Business Services Analyst)</t>
+          <t>Data &amp; Digital Solutions Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>County of Orange</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
+          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
+          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Distinguished Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
+          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>Sfklogix LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1615,146 +1615,6 @@
         </is>
       </c>
       <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Distinguished Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>CloudZero</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>HR -Data Scientist</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Sfklogix LLC</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
         </is>

--- a/results/job_matches_2026-06-06.xlsx
+++ b/results/job_matches_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>Sr Data Engineer- Data Platform &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=18c6ead6041dd8b2</t>
         </is>
       </c>
     </row>
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
+          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New York Blood Center</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rye, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,54 +706,54 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
+          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OpenText xECM Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New York Blood Center</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rye, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DevOps)</t>
+          <t>OpenText xECM Administrator</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ActiveProspect, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,29 +766,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
+          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer (Remote)</t>
+          <t>Senior Platform Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ActiveProspect, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8681c5568e6fb0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
+          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Palm Tree</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Palm Tree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,64 +941,64 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
+          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Kafka Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
+          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
+          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
+          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
+          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Software Engineer II, BS Solutions</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2f921dcd48bc6177</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Tyto Athene</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
+          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9ed805cf135ece</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Business Services Developer (Business Services Analyst)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>County of Orange</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac08d38f082053ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Business Services Developer (Business Services Analyst)</t>
+          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>County of Orange</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
+          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54570e15fbd26f96</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Distinguished Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, Data Platform</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,77 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>HR -Data Scientist</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1. Front-End Web Developer(FE) | Back-End Web Developer (BE) | Content Designer (CD)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Sfklogix LLC</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00720fd3b058f6e4</t>
         </is>
       </c>
     </row>
